--- a/MARSCompetition.xlsx
+++ b/MARSCompetition.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\shalu\source\repos\TASK2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{855BFDC9-E730-4DFE-9D51-A206A896C6F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{474C434C-3DAF-4CB6-B38A-7B15C30D6742}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{A51FEBA8-077E-439E-8EB1-233B9679563D}"/>
   </bookViews>
@@ -910,7 +910,7 @@
 7.click on the submit button </t>
   </si>
   <si>
-    <t>Validate Join Functionality by Registering with an  used email</t>
+    <t>Validate Join Functionality by Registering with an already  used email</t>
   </si>
 </sst>
 </file>
